--- a/data/trans_dic/IP12_R1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023</t>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 9,22</t>
+          <t>1,57; 9,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,24</t>
+          <t>1,14; 5,07</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,72</t>
+          <t>0,64; 8,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,64</t>
+          <t>0,76; 4,17</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,68</t>
+          <t>0,75; 7,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 6,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,31</t>
+          <t>0,8; 5,26</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,16</t>
+          <t>0,27; 3,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,84</t>
+          <t>0,45; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,68</t>
+          <t>0,51; 2,47</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,32</t>
+          <t>0,88; 6,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,07</t>
+          <t>0,88; 6,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,81</t>
+          <t>1,24; 4,76</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,88</t>
+          <t>0,56; 5,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 4,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,33</t>
+          <t>0,42; 3,44</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,19</t>
+          <t>1,33; 3,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,85</t>
+          <t>1,05; 2,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,67</t>
+          <t>1,38; 2,66</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6381</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1645; 9469</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5847</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2750; 12226</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4199</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>612; 7810</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1439; 7941</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1261</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2607</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>390; 3691</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4112</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>927; 6092</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2326</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5598</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>589; 7196</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>992; 7592</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2231; 10756</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7246</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1047; 7242</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1423; 9921</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3503; 13419</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1386</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>386; 3938</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3301</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>590; 4846</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>13983</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>27551</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>8723; 21077</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>7895; 21191</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>19387; 37461</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12_R1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,06</t>
+          <t>1,68; 9,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,07</t>
+          <t>1,19; 5,01</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 8,17</t>
+          <t>0,64; 7,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,17</t>
+          <t>0,73; 4,75</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,12</t>
+          <t>0,75; 7,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,44</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,26</t>
+          <t>0,83; 4,79</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,3</t>
+          <t>0,23; 2,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,48</t>
+          <t>0,45; 3,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,47</t>
+          <t>0,54; 2,47</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,06</t>
+          <t>0,92; 6,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,1</t>
+          <t>0,64; 5,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,76</t>
+          <t>1,21; 4,77</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,72</t>
+          <t>0,56; 5,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,44</t>
+          <t>0,31; 3,63</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,21</t>
+          <t>1,34; 3,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,83</t>
+          <t>1,05; 2,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,66</t>
+          <t>1,42; 2,79</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolor 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1645; 9469</t>
+          <t>1755; 9864</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5847</t>
+          <t>0; 6147</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2750; 12226</t>
+          <t>2873; 12081</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4199</t>
+          <t>0; 3712</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>612; 7810</t>
+          <t>614; 6863</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1439; 7941</t>
+          <t>1389; 9029</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>390; 3691</t>
+          <t>389; 3733</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4112</t>
+          <t>0; 5177</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>927; 6092</t>
+          <t>955; 5543</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>589; 7196</t>
+          <t>503; 6399</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>992; 7592</t>
+          <t>973; 8345</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2231; 10756</t>
+          <t>2351; 10774</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1047; 7242</t>
+          <t>1104; 7651</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1423; 9921</t>
+          <t>1047; 9467</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3503; 13419</t>
+          <t>3427; 13463</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>386; 3938</t>
+          <t>384; 3719</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 2822</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>590; 4846</t>
+          <t>434; 5118</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8723; 21077</t>
+          <t>8824; 21490</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7895; 21191</t>
+          <t>7894; 21153</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19387; 37461</t>
+          <t>19903; 39211</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12_R1_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12_R1_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,44</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>1,86; 9,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,01</t>
+          <t>1,3; 5,75</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>1,03; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,18</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,75</t>
+          <t>0,75; 4,36</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,2</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>0,65; 6,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,79</t>
+          <t>0,77; 5,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,94</t>
+          <t>0,43; 3,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,82</t>
+          <t>0,33; 3,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,47</t>
+          <t>0,63; 3,08</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>2,66%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,41</t>
+          <t>0,97; 6,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,82</t>
+          <t>0,89; 6,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,77</t>
+          <t>1,33; 5,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,4</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,47; 5,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,63</t>
+          <t>0,4; 3,06</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,27</t>
+          <t>1,13; 3,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,82</t>
+          <t>1,4; 3,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,79</t>
+          <t>1,47; 2,81</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>6611</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1755; 9864</t>
+          <t>0; 6301</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6147</t>
+          <t>1918; 9899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2873; 12081</t>
+          <t>2931; 12963</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2612</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3676</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3712</t>
+          <t>939; 7409</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>614; 6863</t>
+          <t>0; 3707</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1389; 9029</t>
+          <t>1411; 8193</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2344</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>389; 3733</t>
+          <t>0; 3514</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5177</t>
+          <t>346; 3628</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>955; 5543</t>
+          <t>847; 5552</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5500</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>503; 6399</t>
+          <t>867; 7776</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>973; 8345</t>
+          <t>597; 6910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2351; 10774</t>
+          <t>2411; 11714</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>7103</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1104; 7651</t>
+          <t>1444; 9694</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1047; 9467</t>
+          <t>1061; 7835</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3427; 13463</t>
+          <t>3562; 13351</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>571</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1785</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>384; 3719</t>
+          <t>0; 2973</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2822</t>
+          <t>334; 3588</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>434; 5118</t>
+          <t>561; 4238</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>13983</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>27019</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8824; 21490</t>
+          <t>7770; 20801</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7894; 21153</t>
+          <t>8718; 21056</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19903; 39211</t>
+          <t>19286; 36837</t>
         </is>
       </c>
     </row>
